--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="212">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -130,6 +130,9 @@
     <t>R</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>U</t>
   </si>
   <si>
@@ -286,9 +289,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t xml:space="preserve">処理結果ステータス	</t>
   </si>
   <si>
@@ -307,7 +307,7 @@
     <t>data</t>
   </si>
   <si>
-    <t>object</t>
+    <t>Object</t>
   </si>
   <si>
     <t>データオブジェクト</t>
@@ -319,16 +319,13 @@
     <t>items</t>
   </si>
   <si>
-    <t>array</t>
+    <t>Array</t>
   </si>
   <si>
     <t>在庫情報の配列</t>
   </si>
   <si>
     <t>stockId</t>
-  </si>
-  <si>
-    <t>integer</t>
   </si>
   <si>
     <t xml:space="preserve">	在庫ID</t>
@@ -674,10 +671,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -743,14 +740,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -770,22 +768,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -799,17 +815,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -823,7 +830,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -831,38 +861,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -879,15 +877,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -920,7 +917,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,7 +1007,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +1067,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,145 +1091,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1284,6 +1281,45 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -1292,10 +1328,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1316,50 +1350,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1374,149 +1371,149 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1814,6 +1811,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1832,9 +1835,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1946,9 +1946,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1981,6 +1987,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2721,7 +2730,7 @@
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.66666666666667" style="4"/>
-    <col min="2" max="2" width="5.11111111111111" style="148" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="151" customWidth="1"/>
     <col min="3" max="3" width="12.3333333333333" style="4" customWidth="1"/>
     <col min="4" max="4" width="10.3333333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="4" customWidth="1"/>
@@ -2734,24 +2743,24 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="150" t="s">
+      <c r="C2" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="150" t="s">
+      <c r="E2" s="153" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="152">
+      <c r="C3" s="155">
         <v>45636</v>
       </c>
       <c r="D3" s="56" t="s">
@@ -2762,397 +2771,397 @@
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="151"/>
-      <c r="C4" s="152"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="155"/>
       <c r="D4" s="56"/>
       <c r="E4" s="57"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="151"/>
-      <c r="C5" s="152"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="155"/>
       <c r="D5" s="56"/>
       <c r="E5" s="57"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="151"/>
+      <c r="B6" s="154"/>
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
       <c r="E6" s="56"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="151"/>
+      <c r="B7" s="154"/>
       <c r="C7" s="56"/>
       <c r="D7" s="56"/>
       <c r="E7" s="56"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="151"/>
+      <c r="B8" s="154"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
       <c r="E8" s="56"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="151"/>
+      <c r="B9" s="154"/>
       <c r="C9" s="56"/>
       <c r="D9" s="56"/>
       <c r="E9" s="56"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="151"/>
+      <c r="B10" s="154"/>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
       <c r="E10" s="56"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="151"/>
+      <c r="B11" s="154"/>
       <c r="C11" s="56"/>
       <c r="D11" s="56"/>
       <c r="E11" s="56"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="151"/>
+      <c r="B12" s="154"/>
       <c r="C12" s="56"/>
       <c r="D12" s="56"/>
       <c r="E12" s="56"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="151"/>
+      <c r="B13" s="154"/>
       <c r="C13" s="56"/>
       <c r="D13" s="56"/>
       <c r="E13" s="56"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="151"/>
+      <c r="B14" s="154"/>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="E14" s="56"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="151"/>
+      <c r="B15" s="154"/>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="151"/>
+      <c r="B16" s="154"/>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="151"/>
+      <c r="B17" s="154"/>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="151"/>
+      <c r="B18" s="154"/>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="151"/>
+      <c r="B19" s="154"/>
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="151"/>
+      <c r="B20" s="154"/>
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="151"/>
+      <c r="B21" s="154"/>
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="E21" s="56"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="151"/>
+      <c r="B22" s="154"/>
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="E22" s="56"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="151"/>
+      <c r="B23" s="154"/>
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="E23" s="56"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="151"/>
+      <c r="B24" s="154"/>
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="E24" s="56"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="151"/>
+      <c r="B25" s="154"/>
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="E25" s="56"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="151"/>
+      <c r="B26" s="154"/>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="E26" s="56"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="151"/>
+      <c r="B27" s="154"/>
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="E27" s="56"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="151"/>
+      <c r="B28" s="154"/>
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="E28" s="56"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="151"/>
+      <c r="B29" s="154"/>
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="E29" s="56"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="151"/>
+      <c r="B30" s="154"/>
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="E30" s="56"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="151"/>
+      <c r="B31" s="154"/>
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="E31" s="56"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="151"/>
+      <c r="B32" s="154"/>
       <c r="C32" s="56"/>
       <c r="D32" s="56"/>
       <c r="E32" s="56"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="151"/>
+      <c r="B33" s="154"/>
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="E33" s="56"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="151"/>
+      <c r="B34" s="154"/>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="E34" s="56"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="151"/>
+      <c r="B35" s="154"/>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="E35" s="56"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="151"/>
+      <c r="B36" s="154"/>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="E36" s="56"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="151"/>
+      <c r="B37" s="154"/>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="E37" s="56"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="151"/>
+      <c r="B38" s="154"/>
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="E38" s="56"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="151"/>
+      <c r="B39" s="154"/>
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="E39" s="56"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="151"/>
+      <c r="B40" s="154"/>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
       <c r="E40" s="56"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="151"/>
+      <c r="B41" s="154"/>
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="E41" s="56"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="151"/>
+      <c r="B42" s="154"/>
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="E42" s="56"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="151"/>
+      <c r="B43" s="154"/>
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="E43" s="56"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="151"/>
+      <c r="B44" s="154"/>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
       <c r="E44" s="56"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="151"/>
+      <c r="B45" s="154"/>
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="E45" s="56"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="151"/>
+      <c r="B46" s="154"/>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="E46" s="56"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="151"/>
+      <c r="B47" s="154"/>
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="E47" s="56"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="151"/>
+      <c r="B48" s="154"/>
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="E48" s="56"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="151"/>
+      <c r="B49" s="154"/>
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="E49" s="56"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="151"/>
+      <c r="B50" s="154"/>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="E50" s="56"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="151"/>
+      <c r="B51" s="154"/>
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="E51" s="56"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="151"/>
+      <c r="B52" s="154"/>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="E52" s="56"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="151"/>
+      <c r="B53" s="154"/>
       <c r="C53" s="56"/>
       <c r="D53" s="56"/>
       <c r="E53" s="56"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="151"/>
+      <c r="B54" s="154"/>
       <c r="C54" s="56"/>
       <c r="D54" s="56"/>
       <c r="E54" s="56"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="151"/>
+      <c r="B55" s="154"/>
       <c r="C55" s="56"/>
       <c r="D55" s="56"/>
       <c r="E55" s="56"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="151"/>
+      <c r="B56" s="154"/>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
       <c r="E56" s="56"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="151"/>
+      <c r="B57" s="154"/>
       <c r="C57" s="56"/>
       <c r="D57" s="56"/>
       <c r="E57" s="56"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="151"/>
+      <c r="B58" s="154"/>
       <c r="C58" s="56"/>
       <c r="D58" s="56"/>
       <c r="E58" s="56"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="151"/>
+      <c r="B59" s="154"/>
       <c r="C59" s="56"/>
       <c r="D59" s="56"/>
       <c r="E59" s="56"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="151"/>
+      <c r="B60" s="154"/>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
       <c r="E60" s="56"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="151"/>
+      <c r="B61" s="154"/>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
       <c r="E61" s="56"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="151"/>
+      <c r="B62" s="154"/>
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
       <c r="E62" s="56"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="151"/>
+      <c r="B63" s="154"/>
       <c r="C63" s="56"/>
       <c r="D63" s="56"/>
       <c r="E63" s="56"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="151"/>
+      <c r="B64" s="154"/>
       <c r="C64" s="56"/>
       <c r="D64" s="56"/>
       <c r="E64" s="56"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="151"/>
+      <c r="B65" s="154"/>
       <c r="C65" s="56"/>
       <c r="D65" s="56"/>
       <c r="E65" s="56"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="151"/>
+      <c r="B66" s="154"/>
       <c r="C66" s="56"/>
       <c r="D66" s="56"/>
       <c r="E66" s="56"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="151"/>
+      <c r="B67" s="154"/>
       <c r="C67" s="56"/>
       <c r="D67" s="56"/>
       <c r="E67" s="56"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="151"/>
+      <c r="B68" s="154"/>
       <c r="C68" s="56"/>
       <c r="D68" s="56"/>
       <c r="E68" s="56"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="151"/>
+      <c r="B69" s="154"/>
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
       <c r="E69" s="56"/>
@@ -3169,11 +3178,11 @@
   <dimension ref="A1:AH25"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="118"/>
-    <col min="21" max="21" width="5.86666666666667" style="118" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="118"/>
-    <col min="34" max="34" width="13.0148148148148" style="118" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="118"/>
+    <col min="1" max="20" width="3.66666666666667" style="119"/>
+    <col min="21" max="21" width="5.86666666666667" style="119" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="119"/>
+    <col min="34" max="34" width="13.0148148148148" style="119" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="119"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -3189,14 +3198,14 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
-      <c r="K1" s="137"/>
+      <c r="K1" s="138"/>
       <c r="L1" s="32" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="33"/>
       <c r="N1" s="33"/>
       <c r="O1" s="33"/>
-      <c r="P1" s="107"/>
+      <c r="P1" s="108"/>
       <c r="Q1" s="34" t="s">
         <v>10</v>
       </c>
@@ -3214,13 +3223,13 @@
       </c>
       <c r="Z1" s="74"/>
       <c r="AA1" s="74"/>
-      <c r="AB1" s="144"/>
+      <c r="AB1" s="147"/>
       <c r="AC1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="153" t="s">
+      <c r="AD1" s="148"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="156" t="s">
         <v>12</v>
       </c>
       <c r="AG1" s="63"/>
@@ -3237,12 +3246,12 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="39"/>
       <c r="M2" s="40"/>
       <c r="N2" s="40"/>
       <c r="O2" s="40"/>
-      <c r="P2" s="108"/>
+      <c r="P2" s="109"/>
       <c r="Q2" s="41"/>
       <c r="R2" s="73"/>
       <c r="S2" s="73"/>
@@ -3254,10 +3263,10 @@
       <c r="Y2" s="43"/>
       <c r="Z2" s="75"/>
       <c r="AA2" s="75"/>
-      <c r="AB2" s="147"/>
+      <c r="AB2" s="150"/>
       <c r="AC2" s="42"/>
-      <c r="AD2" s="102"/>
-      <c r="AE2" s="103"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="105"/>
       <c r="AF2" s="44"/>
       <c r="AG2" s="64"/>
       <c r="AH2" s="64"/>
@@ -3273,14 +3282,14 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="138"/>
+      <c r="K3" s="139"/>
       <c r="L3" s="32" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
       <c r="O3" s="33"/>
-      <c r="P3" s="107"/>
+      <c r="P3" s="108"/>
       <c r="Q3" s="34" t="s">
         <v>14</v>
       </c>
@@ -3298,13 +3307,13 @@
       </c>
       <c r="Z3" s="74"/>
       <c r="AA3" s="74"/>
-      <c r="AB3" s="144"/>
+      <c r="AB3" s="147"/>
       <c r="AC3" s="37" t="s">
         <v>17</v>
       </c>
       <c r="AD3" s="37"/>
       <c r="AE3" s="37"/>
-      <c r="AF3" s="153" t="s">
+      <c r="AF3" s="156" t="s">
         <v>18</v>
       </c>
       <c r="AG3" s="63"/>
@@ -3321,12 +3330,12 @@
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
-      <c r="K4" s="139"/>
+      <c r="K4" s="140"/>
       <c r="L4" s="39"/>
       <c r="M4" s="40"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
-      <c r="P4" s="108"/>
+      <c r="P4" s="109"/>
       <c r="Q4" s="41"/>
       <c r="R4" s="73"/>
       <c r="S4" s="73"/>
@@ -3338,7 +3347,7 @@
       <c r="Y4" s="43"/>
       <c r="Z4" s="75"/>
       <c r="AA4" s="75"/>
-      <c r="AB4" s="147"/>
+      <c r="AB4" s="150"/>
       <c r="AC4" s="37"/>
       <c r="AD4" s="37"/>
       <c r="AE4" s="37"/>
@@ -3347,285 +3356,285 @@
       <c r="AH4" s="64"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="122" t="s">
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
-      <c r="S5" s="140"/>
-      <c r="T5" s="140"/>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-      <c r="W5" s="140"/>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="140"/>
-      <c r="Z5" s="140"/>
-      <c r="AA5" s="140"/>
-      <c r="AB5" s="140"/>
-      <c r="AC5" s="140"/>
-      <c r="AD5" s="140"/>
-      <c r="AE5" s="140"/>
-      <c r="AF5" s="140"/>
-      <c r="AG5" s="140"/>
-      <c r="AH5" s="140"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
+      <c r="R5" s="141"/>
+      <c r="S5" s="141"/>
+      <c r="T5" s="141"/>
+      <c r="U5" s="141"/>
+      <c r="V5" s="141"/>
+      <c r="W5" s="141"/>
+      <c r="X5" s="141"/>
+      <c r="Y5" s="141"/>
+      <c r="Z5" s="141"/>
+      <c r="AA5" s="141"/>
+      <c r="AB5" s="141"/>
+      <c r="AC5" s="141"/>
+      <c r="AD5" s="141"/>
+      <c r="AE5" s="141"/>
+      <c r="AF5" s="141"/>
+      <c r="AG5" s="141"/>
+      <c r="AH5" s="141"/>
     </row>
     <row r="6" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="122" t="s">
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="140"/>
-      <c r="N6" s="140"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="140"/>
-      <c r="R6" s="140"/>
-      <c r="S6" s="140"/>
-      <c r="T6" s="140"/>
-      <c r="U6" s="140"/>
-      <c r="V6" s="140"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="140"/>
-      <c r="Z6" s="140"/>
-      <c r="AA6" s="140"/>
-      <c r="AB6" s="140"/>
-      <c r="AC6" s="140"/>
-      <c r="AD6" s="140"/>
-      <c r="AE6" s="140"/>
-      <c r="AF6" s="140"/>
-      <c r="AG6" s="140"/>
-      <c r="AH6" s="140"/>
+      <c r="I6" s="141"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="141"/>
+      <c r="N6" s="141"/>
+      <c r="O6" s="141"/>
+      <c r="P6" s="141"/>
+      <c r="Q6" s="141"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="141"/>
+      <c r="T6" s="141"/>
+      <c r="U6" s="141"/>
+      <c r="V6" s="141"/>
+      <c r="W6" s="141"/>
+      <c r="X6" s="141"/>
+      <c r="Y6" s="141"/>
+      <c r="Z6" s="141"/>
+      <c r="AA6" s="141"/>
+      <c r="AB6" s="141"/>
+      <c r="AC6" s="141"/>
+      <c r="AD6" s="141"/>
+      <c r="AE6" s="141"/>
+      <c r="AF6" s="141"/>
+      <c r="AG6" s="141"/>
+      <c r="AH6" s="141"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="122" t="s">
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="140"/>
-      <c r="X7" s="140"/>
-      <c r="Y7" s="140"/>
-      <c r="Z7" s="140"/>
-      <c r="AA7" s="140"/>
-      <c r="AB7" s="140"/>
-      <c r="AC7" s="140"/>
-      <c r="AD7" s="140"/>
-      <c r="AE7" s="140"/>
-      <c r="AF7" s="140"/>
-      <c r="AG7" s="140"/>
-      <c r="AH7" s="140"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="141"/>
+      <c r="O7" s="141"/>
+      <c r="P7" s="141"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="141"/>
+      <c r="S7" s="141"/>
+      <c r="T7" s="141"/>
+      <c r="U7" s="141"/>
+      <c r="V7" s="141"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="141"/>
+      <c r="Y7" s="141"/>
+      <c r="Z7" s="141"/>
+      <c r="AA7" s="141"/>
+      <c r="AB7" s="141"/>
+      <c r="AC7" s="141"/>
+      <c r="AD7" s="141"/>
+      <c r="AE7" s="141"/>
+      <c r="AF7" s="141"/>
+      <c r="AG7" s="141"/>
+      <c r="AH7" s="141"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="122" t="s">
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="122"/>
+      <c r="H8" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="140"/>
-      <c r="T8" s="140"/>
-      <c r="U8" s="140"/>
-      <c r="V8" s="140"/>
-      <c r="W8" s="140"/>
-      <c r="X8" s="140"/>
-      <c r="Y8" s="140"/>
-      <c r="Z8" s="140"/>
-      <c r="AA8" s="140"/>
-      <c r="AB8" s="140"/>
-      <c r="AC8" s="140"/>
-      <c r="AD8" s="140"/>
-      <c r="AE8" s="140"/>
-      <c r="AF8" s="140"/>
-      <c r="AG8" s="140"/>
-      <c r="AH8" s="140"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="141"/>
+      <c r="R8" s="141"/>
+      <c r="S8" s="141"/>
+      <c r="T8" s="141"/>
+      <c r="U8" s="141"/>
+      <c r="V8" s="141"/>
+      <c r="W8" s="141"/>
+      <c r="X8" s="141"/>
+      <c r="Y8" s="141"/>
+      <c r="Z8" s="141"/>
+      <c r="AA8" s="141"/>
+      <c r="AB8" s="141"/>
+      <c r="AC8" s="141"/>
+      <c r="AD8" s="141"/>
+      <c r="AE8" s="141"/>
+      <c r="AF8" s="141"/>
+      <c r="AG8" s="141"/>
+      <c r="AH8" s="141"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="119" t="s">
+      <c r="A9" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="122" t="s">
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="140"/>
-      <c r="O9" s="140"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="140"/>
-      <c r="S9" s="140"/>
-      <c r="T9" s="140"/>
-      <c r="U9" s="140"/>
-      <c r="V9" s="140"/>
-      <c r="W9" s="140"/>
-      <c r="X9" s="140"/>
-      <c r="Y9" s="140"/>
-      <c r="Z9" s="140"/>
-      <c r="AA9" s="140"/>
-      <c r="AB9" s="140"/>
-      <c r="AC9" s="140"/>
-      <c r="AD9" s="140"/>
-      <c r="AE9" s="140"/>
-      <c r="AF9" s="140"/>
-      <c r="AG9" s="140"/>
-      <c r="AH9" s="140"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="141"/>
+      <c r="P9" s="141"/>
+      <c r="Q9" s="141"/>
+      <c r="R9" s="141"/>
+      <c r="S9" s="141"/>
+      <c r="T9" s="141"/>
+      <c r="U9" s="141"/>
+      <c r="V9" s="141"/>
+      <c r="W9" s="141"/>
+      <c r="X9" s="141"/>
+      <c r="Y9" s="141"/>
+      <c r="Z9" s="141"/>
+      <c r="AA9" s="141"/>
+      <c r="AB9" s="141"/>
+      <c r="AC9" s="141"/>
+      <c r="AD9" s="141"/>
+      <c r="AE9" s="141"/>
+      <c r="AF9" s="141"/>
+      <c r="AG9" s="141"/>
+      <c r="AH9" s="141"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="126" t="s">
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="141"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="141"/>
-      <c r="O10" s="141"/>
-      <c r="P10" s="141"/>
-      <c r="Q10" s="141"/>
-      <c r="R10" s="141"/>
-      <c r="S10" s="141"/>
-      <c r="T10" s="141"/>
-      <c r="U10" s="141"/>
-      <c r="V10" s="141"/>
-      <c r="W10" s="141"/>
-      <c r="X10" s="141"/>
-      <c r="Y10" s="141"/>
-      <c r="Z10" s="141"/>
-      <c r="AA10" s="141"/>
-      <c r="AB10" s="141"/>
-      <c r="AC10" s="141"/>
-      <c r="AD10" s="141"/>
-      <c r="AE10" s="141"/>
-      <c r="AF10" s="141"/>
-      <c r="AG10" s="141"/>
-      <c r="AH10" s="141"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="142"/>
+      <c r="U10" s="142"/>
+      <c r="V10" s="142"/>
+      <c r="W10" s="142"/>
+      <c r="X10" s="142"/>
+      <c r="Y10" s="142"/>
+      <c r="Z10" s="142"/>
+      <c r="AA10" s="142"/>
+      <c r="AB10" s="142"/>
+      <c r="AC10" s="142"/>
+      <c r="AD10" s="142"/>
+      <c r="AE10" s="142"/>
+      <c r="AF10" s="142"/>
+      <c r="AG10" s="142"/>
+      <c r="AH10" s="142"/>
     </row>
     <row r="11" s="67" customFormat="1" customHeight="1" spans="1:34">
       <c r="A11" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="127"/>
-      <c r="W11" s="127"/>
-      <c r="X11" s="127"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="127"/>
-      <c r="AB11" s="127"/>
-      <c r="AC11" s="127"/>
-      <c r="AD11" s="127"/>
-      <c r="AE11" s="127"/>
-      <c r="AF11" s="127"/>
-      <c r="AG11" s="127"/>
-      <c r="AH11" s="127"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="128"/>
+      <c r="T11" s="128"/>
+      <c r="U11" s="128"/>
+      <c r="V11" s="128"/>
+      <c r="W11" s="128"/>
+      <c r="X11" s="128"/>
+      <c r="Y11" s="128"/>
+      <c r="Z11" s="128"/>
+      <c r="AA11" s="128"/>
+      <c r="AB11" s="128"/>
+      <c r="AC11" s="128"/>
+      <c r="AD11" s="128"/>
+      <c r="AE11" s="128"/>
+      <c r="AF11" s="128"/>
+      <c r="AG11" s="128"/>
+      <c r="AH11" s="128"/>
     </row>
     <row r="12" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A12" s="128"/>
+      <c r="A12" s="129"/>
       <c r="B12" s="71"/>
       <c r="C12" s="71"/>
       <c r="D12" s="71"/>
@@ -3661,7 +3670,7 @@
       <c r="AH12" s="71"/>
     </row>
     <row r="13" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A13" s="128"/>
+      <c r="A13" s="129"/>
       <c r="B13" s="71"/>
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
@@ -3697,7 +3706,7 @@
       <c r="AH13" s="71"/>
     </row>
     <row r="14" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A14" s="128"/>
+      <c r="A14" s="129"/>
       <c r="B14" s="71"/>
       <c r="C14" s="71"/>
       <c r="D14" s="71"/>
@@ -3733,7 +3742,7 @@
       <c r="AH14" s="71"/>
     </row>
     <row r="15" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A15" s="128"/>
+      <c r="A15" s="129"/>
       <c r="B15" s="71"/>
       <c r="C15" s="71"/>
       <c r="D15" s="71"/>
@@ -3769,7 +3778,7 @@
       <c r="AH15" s="71"/>
     </row>
     <row r="16" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A16" s="128"/>
+      <c r="A16" s="129"/>
       <c r="B16" s="71"/>
       <c r="C16" s="71"/>
       <c r="D16" s="71"/>
@@ -3805,7 +3814,7 @@
       <c r="AH16" s="71"/>
     </row>
     <row r="17" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A17" s="128"/>
+      <c r="A17" s="129"/>
       <c r="B17" s="71"/>
       <c r="C17" s="71"/>
       <c r="D17" s="71"/>
@@ -3841,7 +3850,7 @@
       <c r="AH17" s="71"/>
     </row>
     <row r="18" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A18" s="128"/>
+      <c r="A18" s="129"/>
       <c r="B18" s="71"/>
       <c r="C18" s="71"/>
       <c r="D18" s="71"/>
@@ -3877,7 +3886,7 @@
       <c r="AH18" s="71"/>
     </row>
     <row r="19" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A19" s="128"/>
+      <c r="A19" s="129"/>
       <c r="B19" s="71"/>
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
@@ -3913,7 +3922,7 @@
       <c r="AH19" s="71"/>
     </row>
     <row r="20" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A20" s="128"/>
+      <c r="A20" s="129"/>
       <c r="B20" s="71"/>
       <c r="C20" s="71"/>
       <c r="D20" s="71"/>
@@ -3949,7 +3958,7 @@
       <c r="AH20" s="71"/>
     </row>
     <row r="21" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A21" s="128"/>
+      <c r="A21" s="129"/>
       <c r="B21" s="71"/>
       <c r="C21" s="71"/>
       <c r="D21" s="71"/>
@@ -3985,7 +3994,7 @@
       <c r="AH21" s="71"/>
     </row>
     <row r="22" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A22" s="128"/>
+      <c r="A22" s="129"/>
       <c r="B22" s="71"/>
       <c r="C22" s="71"/>
       <c r="D22" s="71"/>
@@ -4021,133 +4030,135 @@
       <c r="AH22" s="71"/>
     </row>
     <row r="23" s="67" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="129"/>
-      <c r="B23" s="106"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="106"/>
-      <c r="R23" s="106"/>
-      <c r="S23" s="106"/>
-      <c r="T23" s="106"/>
-      <c r="U23" s="106"/>
-      <c r="V23" s="106"/>
-      <c r="W23" s="106"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="106"/>
-      <c r="Z23" s="106"/>
-      <c r="AA23" s="106"/>
-      <c r="AB23" s="106"/>
-      <c r="AC23" s="106"/>
-      <c r="AD23" s="106"/>
-      <c r="AE23" s="106"/>
-      <c r="AF23" s="106"/>
-      <c r="AG23" s="106"/>
-      <c r="AH23" s="106"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="107"/>
+      <c r="O23" s="107"/>
+      <c r="P23" s="107"/>
+      <c r="Q23" s="107"/>
+      <c r="R23" s="107"/>
+      <c r="S23" s="107"/>
+      <c r="T23" s="107"/>
+      <c r="U23" s="107"/>
+      <c r="V23" s="107"/>
+      <c r="W23" s="107"/>
+      <c r="X23" s="107"/>
+      <c r="Y23" s="107"/>
+      <c r="Z23" s="107"/>
+      <c r="AA23" s="107"/>
+      <c r="AB23" s="107"/>
+      <c r="AC23" s="107"/>
+      <c r="AD23" s="107"/>
+      <c r="AE23" s="107"/>
+      <c r="AF23" s="107"/>
+      <c r="AG23" s="107"/>
+      <c r="AH23" s="107"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="130" t="s">
+      <c r="A24" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="131"/>
-      <c r="C24" s="130" t="s">
+      <c r="B24" s="132"/>
+      <c r="C24" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="132"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="142" t="s">
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="142" t="s">
+      <c r="L24" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="142" t="s">
+      <c r="M24" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="130" t="s">
+      <c r="N24" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="132"/>
-      <c r="P24" s="132"/>
-      <c r="Q24" s="132"/>
-      <c r="R24" s="132"/>
-      <c r="S24" s="132"/>
-      <c r="T24" s="132"/>
-      <c r="U24" s="132"/>
-      <c r="V24" s="132"/>
-      <c r="W24" s="132"/>
-      <c r="X24" s="132"/>
-      <c r="Y24" s="132"/>
-      <c r="Z24" s="132"/>
-      <c r="AA24" s="132"/>
-      <c r="AB24" s="132"/>
-      <c r="AC24" s="132"/>
-      <c r="AD24" s="132"/>
-      <c r="AE24" s="132"/>
-      <c r="AF24" s="132"/>
-      <c r="AG24" s="132"/>
-      <c r="AH24" s="132"/>
+      <c r="O24" s="144" t="s">
+        <v>37</v>
+      </c>
+      <c r="P24" s="144"/>
+      <c r="Q24" s="144"/>
+      <c r="R24" s="144"/>
+      <c r="S24" s="144"/>
+      <c r="T24" s="144"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="144"/>
+      <c r="W24" s="144"/>
+      <c r="X24" s="144"/>
+      <c r="Y24" s="144"/>
+      <c r="Z24" s="144"/>
+      <c r="AA24" s="144"/>
+      <c r="AB24" s="144"/>
+      <c r="AC24" s="144"/>
+      <c r="AD24" s="144"/>
+      <c r="AE24" s="144"/>
+      <c r="AF24" s="144"/>
+      <c r="AG24" s="144"/>
+      <c r="AH24" s="144"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="133">
+      <c r="A25" s="134">
         <v>1</v>
       </c>
-      <c r="B25" s="134"/>
-      <c r="C25" s="135" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="143" t="s">
+      <c r="B25" s="135"/>
+      <c r="C25" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="L25" s="143"/>
-      <c r="M25" s="143"/>
-      <c r="N25" s="135"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="136"/>
-      <c r="Q25" s="136"/>
-      <c r="R25" s="136"/>
-      <c r="S25" s="136"/>
-      <c r="T25" s="136"/>
-      <c r="U25" s="136"/>
-      <c r="V25" s="136"/>
-      <c r="W25" s="136"/>
-      <c r="X25" s="136"/>
-      <c r="Y25" s="136"/>
-      <c r="Z25" s="136"/>
-      <c r="AA25" s="136"/>
-      <c r="AB25" s="136"/>
-      <c r="AC25" s="136"/>
-      <c r="AD25" s="136"/>
-      <c r="AE25" s="136"/>
-      <c r="AF25" s="136"/>
-      <c r="AG25" s="136"/>
-      <c r="AH25" s="136"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137"/>
+      <c r="K25" s="145" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" s="145"/>
+      <c r="M25" s="145"/>
+      <c r="N25" s="146"/>
+      <c r="O25" s="145"/>
+      <c r="P25" s="145"/>
+      <c r="Q25" s="145"/>
+      <c r="R25" s="145"/>
+      <c r="S25" s="145"/>
+      <c r="T25" s="145"/>
+      <c r="U25" s="145"/>
+      <c r="V25" s="145"/>
+      <c r="W25" s="145"/>
+      <c r="X25" s="145"/>
+      <c r="Y25" s="145"/>
+      <c r="Z25" s="145"/>
+      <c r="AA25" s="145"/>
+      <c r="AB25" s="145"/>
+      <c r="AC25" s="145"/>
+      <c r="AD25" s="145"/>
+      <c r="AE25" s="145"/>
+      <c r="AF25" s="145"/>
+      <c r="AG25" s="145"/>
+      <c r="AH25" s="145"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="H5:AH5"/>
     <mergeCell ref="A6:G6"/>
@@ -4163,8 +4174,9 @@
     <mergeCell ref="A11:AH11"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="N24:AH24"/>
+    <mergeCell ref="O24:AH24"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
     <mergeCell ref="V3:X4"/>
     <mergeCell ref="AC3:AE4"/>
     <mergeCell ref="AF3:AH4"/>
@@ -4209,7 +4221,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:25">
       <c r="A1" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4225,7 +4237,7 @@
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
       <c r="M1" s="33"/>
-      <c r="N1" s="107"/>
+      <c r="N1" s="108"/>
       <c r="O1" s="34" t="s">
         <v>10</v>
       </c>
@@ -4243,7 +4255,7 @@
       <c r="W1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="153" t="s">
+      <c r="X1" s="156" t="s">
         <v>12</v>
       </c>
       <c r="Y1" s="63"/>
@@ -4262,7 +4274,7 @@
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
       <c r="M2" s="40"/>
-      <c r="N2" s="108"/>
+      <c r="N2" s="109"/>
       <c r="O2" s="41"/>
       <c r="P2" s="73"/>
       <c r="Q2" s="73"/>
@@ -4291,7 +4303,7 @@
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
       <c r="M3" s="33"/>
-      <c r="N3" s="107"/>
+      <c r="N3" s="108"/>
       <c r="O3" s="34" t="s">
         <v>14</v>
       </c>
@@ -4309,7 +4321,7 @@
       <c r="W3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="153" t="s">
+      <c r="X3" s="156" t="s">
         <v>18</v>
       </c>
       <c r="Y3" s="63"/>
@@ -4328,7 +4340,7 @@
       <c r="K4" s="40"/>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
-      <c r="N4" s="108"/>
+      <c r="N4" s="109"/>
       <c r="O4" s="41"/>
       <c r="P4" s="73"/>
       <c r="Q4" s="73"/>
@@ -4343,7 +4355,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -4356,7 +4368,7 @@
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
@@ -4370,7 +4382,7 @@
       <c r="R5" s="13"/>
       <c r="S5" s="13"/>
       <c r="T5" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U5" s="13" t="s">
         <v>29</v>
@@ -4382,7 +4394,7 @@
     </row>
     <row r="6" s="65" customFormat="1" customHeight="1" spans="1:1">
       <c r="A6" s="68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" s="65" customFormat="1" ht="23" customHeight="1" spans="1:25">
@@ -4390,7 +4402,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37"/>
@@ -4399,52 +4411,52 @@
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
       <c r="I7" s="37"/>
-      <c r="J7" s="109" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="110" t="s">
+      <c r="J7" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="112"/>
+      <c r="K7" s="111" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="113"/>
       <c r="O7" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P7" s="37"/>
       <c r="Q7" s="37"/>
       <c r="R7" s="37"/>
       <c r="S7" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T7" s="37"/>
-      <c r="U7" s="110" t="s">
-        <v>49</v>
-      </c>
-      <c r="V7" s="111"/>
-      <c r="W7" s="111"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="111"/>
+      <c r="U7" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="V7" s="112"/>
+      <c r="W7" s="112"/>
+      <c r="X7" s="112"/>
+      <c r="Y7" s="112"/>
     </row>
     <row r="8" s="65" customFormat="1" customHeight="1" spans="1:25">
       <c r="A8" s="83">
         <v>1</v>
       </c>
-      <c r="B8" s="105" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105" t="s">
+      <c r="B8" s="99" t="s">
         <v>51</v>
       </c>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99" t="s">
+        <v>52</v>
+      </c>
       <c r="K8" s="91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L8" s="90"/>
       <c r="M8" s="90"/>
@@ -4456,11 +4468,11 @@
       <c r="Q8" s="83"/>
       <c r="R8" s="83"/>
       <c r="S8" s="83" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T8" s="83"/>
       <c r="U8" s="91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V8" s="90"/>
       <c r="W8" s="90"/>
@@ -4472,7 +4484,7 @@
     </row>
     <row r="10" s="65" customFormat="1" customHeight="1" spans="1:1">
       <c r="A10" s="68" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" s="65" customFormat="1" ht="28" customHeight="1" spans="1:25">
@@ -4480,125 +4492,125 @@
         <v>31</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="37"/>
       <c r="D11" s="37"/>
       <c r="E11" s="37"/>
       <c r="F11" s="37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
       <c r="K11" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
       <c r="O11" s="37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P11" s="37"/>
-      <c r="Q11" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="109"/>
-      <c r="S11" s="109"/>
-      <c r="T11" s="109"/>
+      <c r="Q11" s="110" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="110"/>
+      <c r="S11" s="110"/>
+      <c r="T11" s="110"/>
       <c r="U11" s="37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V11" s="37"/>
       <c r="W11" s="37"/>
-      <c r="X11" s="110" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y11" s="111"/>
+      <c r="X11" s="111" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y11" s="112"/>
     </row>
     <row r="12" s="65" customFormat="1" ht="16.5" spans="1:25">
       <c r="A12" s="83">
         <v>1</v>
       </c>
       <c r="B12" s="83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="83"/>
       <c r="D12" s="83"/>
       <c r="E12" s="83"/>
       <c r="F12" s="83" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="83"/>
       <c r="H12" s="83"/>
       <c r="I12" s="83"/>
       <c r="J12" s="83"/>
       <c r="K12" s="91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L12" s="90"/>
       <c r="M12" s="90"/>
       <c r="N12" s="97"/>
-      <c r="O12" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="154" t="s">
-        <v>60</v>
+      <c r="O12" s="114" t="s">
+        <v>52</v>
+      </c>
+      <c r="P12" s="115"/>
+      <c r="Q12" s="157" t="s">
+        <v>61</v>
       </c>
       <c r="R12" s="83"/>
       <c r="S12" s="83"/>
       <c r="T12" s="83"/>
-      <c r="U12" s="115" t="s">
-        <v>63</v>
+      <c r="U12" s="116" t="s">
+        <v>64</v>
       </c>
       <c r="V12" s="83"/>
       <c r="W12" s="83"/>
       <c r="X12" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y12" s="116"/>
+        <v>65</v>
+      </c>
+      <c r="Y12" s="117"/>
     </row>
     <row r="13" s="65" customFormat="1" ht="16.5" spans="1:25">
       <c r="A13" s="83">
         <v>2</v>
       </c>
       <c r="B13" s="83" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="83"/>
       <c r="D13" s="83"/>
       <c r="E13" s="83"/>
       <c r="F13" s="83" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="83"/>
       <c r="H13" s="83"/>
       <c r="I13" s="83"/>
       <c r="J13" s="83"/>
       <c r="K13" s="91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L13" s="90"/>
       <c r="M13" s="90"/>
       <c r="N13" s="97"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="154" t="s">
-        <v>67</v>
+      <c r="O13" s="114"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="157" t="s">
+        <v>68</v>
       </c>
       <c r="R13" s="83"/>
       <c r="S13" s="83"/>
       <c r="T13" s="83"/>
-      <c r="U13" s="115" t="s">
-        <v>63</v>
+      <c r="U13" s="116" t="s">
+        <v>64</v>
       </c>
       <c r="V13" s="83"/>
       <c r="W13" s="83"/>
       <c r="X13" s="83" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y13" s="83"/>
     </row>
@@ -4607,80 +4619,80 @@
         <v>3</v>
       </c>
       <c r="B14" s="83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="83"/>
       <c r="D14" s="83"/>
       <c r="E14" s="83"/>
       <c r="F14" s="83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="83"/>
       <c r="H14" s="83"/>
       <c r="I14" s="83"/>
       <c r="J14" s="83"/>
       <c r="K14" s="91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L14" s="90"/>
       <c r="M14" s="90"/>
       <c r="N14" s="97"/>
-      <c r="O14" s="113"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="154" t="s">
-        <v>67</v>
+      <c r="O14" s="114"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="157" t="s">
+        <v>68</v>
       </c>
       <c r="R14" s="83"/>
       <c r="S14" s="83"/>
       <c r="T14" s="83"/>
-      <c r="U14" s="115" t="s">
-        <v>63</v>
+      <c r="U14" s="116" t="s">
+        <v>64</v>
       </c>
       <c r="V14" s="83"/>
       <c r="W14" s="83"/>
       <c r="X14" s="92">
         <v>1</v>
       </c>
-      <c r="Y14" s="117"/>
+      <c r="Y14" s="118"/>
     </row>
     <row r="15" s="65" customFormat="1" ht="16.5" spans="1:25">
       <c r="A15" s="83">
         <v>4</v>
       </c>
       <c r="B15" s="83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="83"/>
       <c r="D15" s="83"/>
       <c r="E15" s="83"/>
       <c r="F15" s="83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" s="83"/>
       <c r="H15" s="83"/>
       <c r="I15" s="83"/>
       <c r="J15" s="83"/>
       <c r="K15" s="91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L15" s="90"/>
       <c r="M15" s="90"/>
       <c r="N15" s="97"/>
-      <c r="O15" s="113"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="154" t="s">
-        <v>70</v>
+      <c r="O15" s="114"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="157" t="s">
+        <v>71</v>
       </c>
       <c r="R15" s="83"/>
       <c r="S15" s="83"/>
       <c r="T15" s="83"/>
       <c r="U15" s="83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V15" s="83"/>
       <c r="W15" s="83"/>
       <c r="X15" s="91" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y15" s="97"/>
     </row>
@@ -4689,34 +4701,34 @@
         <v>5</v>
       </c>
       <c r="B16" s="83" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="83"/>
       <c r="D16" s="83"/>
       <c r="E16" s="83"/>
       <c r="F16" s="83" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="83"/>
       <c r="H16" s="83"/>
       <c r="I16" s="83"/>
       <c r="J16" s="83"/>
       <c r="K16" s="91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L16" s="90"/>
       <c r="M16" s="90"/>
       <c r="N16" s="97"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="154" t="s">
-        <v>77</v>
+      <c r="O16" s="114"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="157" t="s">
+        <v>78</v>
       </c>
       <c r="R16" s="83"/>
       <c r="S16" s="83"/>
       <c r="T16" s="83"/>
       <c r="U16" s="83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V16" s="83"/>
       <c r="W16" s="83"/>
@@ -4730,34 +4742,34 @@
         <v>6</v>
       </c>
       <c r="B17" s="83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="83"/>
       <c r="D17" s="83"/>
       <c r="E17" s="83"/>
       <c r="F17" s="83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" s="83"/>
       <c r="H17" s="83"/>
       <c r="I17" s="83"/>
       <c r="J17" s="83"/>
       <c r="K17" s="91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L17" s="90"/>
       <c r="M17" s="90"/>
       <c r="N17" s="97"/>
-      <c r="O17" s="113"/>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="154" t="s">
-        <v>81</v>
+      <c r="O17" s="114"/>
+      <c r="P17" s="115"/>
+      <c r="Q17" s="157" t="s">
+        <v>82</v>
       </c>
       <c r="R17" s="83"/>
       <c r="S17" s="83"/>
       <c r="T17" s="83"/>
       <c r="U17" s="83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V17" s="83"/>
       <c r="W17" s="83"/>
@@ -4770,31 +4782,31 @@
       <c r="A18" s="69"/>
     </row>
     <row r="19" customHeight="1" spans="1:25">
-      <c r="A19" s="106"/>
-      <c r="B19" s="106"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="106"/>
-      <c r="T19" s="106"/>
-      <c r="U19" s="106"/>
-      <c r="V19" s="106"/>
-      <c r="W19" s="106"/>
-      <c r="X19" s="106"/>
-      <c r="Y19" s="106"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="107"/>
+      <c r="P19" s="107"/>
+      <c r="Q19" s="107"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="107"/>
+      <c r="T19" s="107"/>
+      <c r="U19" s="107"/>
+      <c r="V19" s="107"/>
+      <c r="W19" s="107"/>
+      <c r="X19" s="107"/>
+      <c r="Y19" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="77">
@@ -4907,7 +4919,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:22">
       <c r="A1" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4938,10 +4950,10 @@
       <c r="T1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="153" t="s">
+      <c r="U1" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="99"/>
+      <c r="V1" s="101"/>
     </row>
     <row r="2" customHeight="1" spans="1:22">
       <c r="A2" s="8"/>
@@ -4965,7 +4977,7 @@
       <c r="S2" s="75"/>
       <c r="T2" s="42"/>
       <c r="U2" s="44"/>
-      <c r="V2" s="100"/>
+      <c r="V2" s="102"/>
     </row>
     <row r="3" customHeight="1" spans="1:22">
       <c r="A3" s="8"/>
@@ -4998,10 +5010,10 @@
       <c r="T3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="153" t="s">
+      <c r="U3" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="99"/>
+      <c r="V3" s="101"/>
     </row>
     <row r="4" customHeight="1" spans="1:22">
       <c r="A4" s="10"/>
@@ -5025,11 +5037,11 @@
       <c r="S4" s="75"/>
       <c r="T4" s="37"/>
       <c r="U4" s="44"/>
-      <c r="V4" s="100"/>
+      <c r="V4" s="102"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -5041,7 +5053,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
@@ -5053,7 +5065,7 @@
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>29</v>
@@ -5089,7 +5101,7 @@
     </row>
     <row r="7" s="65" customFormat="1" ht="16.5" spans="1:22">
       <c r="A7" s="80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" s="81"/>
       <c r="C7" s="81"/>
@@ -5111,14 +5123,14 @@
       <c r="S7" s="81"/>
       <c r="T7" s="81"/>
       <c r="U7" s="81"/>
-      <c r="V7" s="101"/>
+      <c r="V7" s="103"/>
     </row>
     <row r="8" s="65" customFormat="1" ht="16.5" spans="1:22">
       <c r="A8" s="82" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="82"/>
       <c r="D8" s="82"/>
@@ -5127,34 +5139,34 @@
       <c r="G8" s="82"/>
       <c r="H8" s="82"/>
       <c r="I8" s="82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J8" s="82"/>
       <c r="K8" s="82"/>
       <c r="L8" s="82"/>
       <c r="M8" s="82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N8" s="82"/>
       <c r="O8" s="82"/>
       <c r="P8" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q8" s="98"/>
       <c r="R8" s="98"/>
       <c r="S8" s="98"/>
       <c r="T8" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" s="102"/>
-      <c r="V8" s="103"/>
+        <v>85</v>
+      </c>
+      <c r="U8" s="104"/>
+      <c r="V8" s="105"/>
     </row>
     <row r="9" s="65" customFormat="1" customHeight="1" spans="1:22">
       <c r="A9" s="83">
         <v>1</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -5162,18 +5174,18 @@
       <c r="F9" s="85"/>
       <c r="G9" s="85"/>
       <c r="H9" s="85"/>
-      <c r="I9" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="154" t="s">
+      <c r="I9" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="157" t="s">
         <v>87</v>
       </c>
       <c r="Q9" s="83"/>
@@ -5198,18 +5210,18 @@
       <c r="F10" s="85"/>
       <c r="G10" s="85"/>
       <c r="H10" s="85"/>
-      <c r="I10" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="154" t="s">
+      <c r="I10" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="157" t="s">
         <v>90</v>
       </c>
       <c r="Q10" s="83"/>
@@ -5240,18 +5252,18 @@
       <c r="J11" s="83"/>
       <c r="K11" s="83"/>
       <c r="L11" s="83"/>
-      <c r="M11" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="154" t="s">
+      <c r="M11" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="157" t="s">
         <v>94</v>
       </c>
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
       <c r="S11" s="83"/>
-      <c r="T11" s="154" t="s">
+      <c r="T11" s="157" t="s">
         <v>95</v>
       </c>
       <c r="U11" s="83"/>
@@ -5276,18 +5288,18 @@
       <c r="J12" s="83"/>
       <c r="K12" s="83"/>
       <c r="L12" s="83"/>
-      <c r="M12" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="154" t="s">
+      <c r="M12" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="157" t="s">
         <v>98</v>
       </c>
       <c r="Q12" s="83"/>
       <c r="R12" s="83"/>
       <c r="S12" s="83"/>
-      <c r="T12" s="154" t="s">
+      <c r="T12" s="157" t="s">
         <v>95</v>
       </c>
       <c r="U12" s="83"/>
@@ -5306,19 +5318,19 @@
       <c r="F13" s="91"/>
       <c r="G13" s="90"/>
       <c r="H13" s="90"/>
-      <c r="I13" s="83" t="s">
+      <c r="I13" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="99"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="157" t="s">
         <v>100</v>
-      </c>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="154" t="s">
-        <v>101</v>
       </c>
       <c r="Q13" s="83"/>
       <c r="R13" s="83"/>
@@ -5337,28 +5349,28 @@
       <c r="C14" s="87"/>
       <c r="D14" s="87"/>
       <c r="E14" s="83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="91"/>
       <c r="G14" s="90"/>
       <c r="H14" s="90"/>
-      <c r="I14" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="154" t="s">
-        <v>103</v>
+      <c r="I14" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="99"/>
+      <c r="P14" s="157" t="s">
+        <v>102</v>
       </c>
       <c r="Q14" s="83"/>
       <c r="R14" s="83"/>
       <c r="S14" s="83"/>
       <c r="T14" s="83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U14" s="83"/>
       <c r="V14" s="83"/>
@@ -5371,28 +5383,28 @@
       <c r="C15" s="87"/>
       <c r="D15" s="87"/>
       <c r="E15" s="83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F15" s="91"/>
       <c r="G15" s="90"/>
       <c r="H15" s="90"/>
-      <c r="I15" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="154" t="s">
-        <v>106</v>
+      <c r="I15" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="90"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="97"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="157" t="s">
+        <v>105</v>
       </c>
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
       <c r="S15" s="83"/>
       <c r="T15" s="83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U15" s="83"/>
       <c r="V15" s="83"/>
@@ -5405,28 +5417,28 @@
       <c r="C16" s="87"/>
       <c r="D16" s="87"/>
       <c r="E16" s="83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F16" s="91"/>
       <c r="G16" s="90"/>
       <c r="H16" s="90"/>
-      <c r="I16" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="154" t="s">
-        <v>70</v>
+      <c r="I16" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="157" t="s">
+        <v>71</v>
       </c>
       <c r="Q16" s="83"/>
       <c r="R16" s="83"/>
       <c r="S16" s="83"/>
       <c r="T16" s="83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U16" s="83"/>
       <c r="V16" s="83"/>
@@ -5439,22 +5451,22 @@
       <c r="C17" s="87"/>
       <c r="D17" s="87"/>
       <c r="E17" s="83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" s="91"/>
       <c r="G17" s="90"/>
       <c r="H17" s="90"/>
-      <c r="I17" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="154" t="s">
-        <v>111</v>
+      <c r="I17" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="157" t="s">
+        <v>110</v>
       </c>
       <c r="Q17" s="83"/>
       <c r="R17" s="83"/>
@@ -5473,28 +5485,28 @@
       <c r="C18" s="87"/>
       <c r="D18" s="87"/>
       <c r="E18" s="83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" s="91"/>
       <c r="G18" s="90"/>
       <c r="H18" s="90"/>
-      <c r="I18" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="154" t="s">
-        <v>113</v>
+      <c r="I18" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="157" t="s">
+        <v>112</v>
       </c>
       <c r="Q18" s="83"/>
       <c r="R18" s="83"/>
       <c r="S18" s="83"/>
       <c r="T18" s="83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U18" s="83"/>
       <c r="V18" s="83"/>
@@ -5506,25 +5518,25 @@
       <c r="B19" s="92"/>
       <c r="C19" s="92"/>
       <c r="D19" s="83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E19" s="83"/>
       <c r="F19" s="91"/>
       <c r="G19" s="90"/>
       <c r="H19" s="90"/>
-      <c r="I19" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="154" t="s">
-        <v>116</v>
+      <c r="I19" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="157" t="s">
+        <v>115</v>
       </c>
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
@@ -5561,7 +5573,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:22">
       <c r="A21" s="93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="94"/>
       <c r="C21" s="94"/>
@@ -5583,14 +5595,14 @@
       <c r="S21" s="94"/>
       <c r="T21" s="94"/>
       <c r="U21" s="94"/>
-      <c r="V21" s="104"/>
+      <c r="V21" s="106"/>
     </row>
     <row r="22" customHeight="1" spans="1:22">
       <c r="A22" s="82" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="82"/>
       <c r="D22" s="82"/>
@@ -5599,27 +5611,27 @@
       <c r="G22" s="82"/>
       <c r="H22" s="82"/>
       <c r="I22" s="82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J22" s="82"/>
       <c r="K22" s="82"/>
       <c r="L22" s="82"/>
       <c r="M22" s="82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N22" s="82"/>
       <c r="O22" s="82"/>
       <c r="P22" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q22" s="98"/>
       <c r="R22" s="98"/>
       <c r="S22" s="98"/>
       <c r="T22" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="U22" s="102"/>
-      <c r="V22" s="103"/>
+        <v>85</v>
+      </c>
+      <c r="U22" s="104"/>
+      <c r="V22" s="105"/>
     </row>
     <row r="23" s="77" customFormat="1" customHeight="1" spans="1:22">
       <c r="A23" s="83">
@@ -5634,25 +5646,25 @@
       <c r="F23" s="85"/>
       <c r="G23" s="85"/>
       <c r="H23" s="85"/>
-      <c r="I23" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="154" t="s">
+      <c r="I23" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="99"/>
+      <c r="O23" s="99"/>
+      <c r="P23" s="157" t="s">
         <v>87</v>
       </c>
       <c r="Q23" s="83"/>
       <c r="R23" s="83"/>
       <c r="S23" s="83"/>
       <c r="T23" s="83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U23" s="83"/>
       <c r="V23" s="83"/>
@@ -5662,7 +5674,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="85"/>
       <c r="D24" s="85"/>
@@ -5670,25 +5682,25 @@
       <c r="F24" s="85"/>
       <c r="G24" s="85"/>
       <c r="H24" s="85"/>
-      <c r="I24" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="154" t="s">
-        <v>119</v>
+      <c r="I24" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N24" s="99"/>
+      <c r="O24" s="99"/>
+      <c r="P24" s="157" t="s">
+        <v>118</v>
       </c>
       <c r="Q24" s="83"/>
       <c r="R24" s="83"/>
       <c r="S24" s="83"/>
       <c r="T24" s="83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U24" s="83"/>
       <c r="V24" s="83"/>
@@ -5698,7 +5710,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="95" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
@@ -5706,32 +5718,37 @@
       <c r="F25" s="85"/>
       <c r="G25" s="85"/>
       <c r="H25" s="96"/>
-      <c r="I25" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
+      <c r="I25" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N25" s="99"/>
+      <c r="O25" s="99"/>
       <c r="P25" s="83" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q25" s="83"/>
       <c r="R25" s="83"/>
       <c r="S25" s="83"/>
       <c r="T25" s="83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U25" s="83"/>
       <c r="V25" s="83"/>
     </row>
+    <row r="26" customHeight="1" spans="13:15">
+      <c r="M26" s="100"/>
+      <c r="N26" s="100"/>
+      <c r="O26" s="100"/>
+    </row>
     <row r="27" customHeight="1" spans="1:22">
       <c r="A27" s="93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B27" s="94"/>
       <c r="C27" s="94"/>
@@ -5753,14 +5770,14 @@
       <c r="S27" s="94"/>
       <c r="T27" s="94"/>
       <c r="U27" s="94"/>
-      <c r="V27" s="104"/>
+      <c r="V27" s="106"/>
     </row>
     <row r="28" customHeight="1" spans="1:22">
       <c r="A28" s="82" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="82"/>
       <c r="D28" s="82"/>
@@ -5769,34 +5786,34 @@
       <c r="G28" s="82"/>
       <c r="H28" s="82"/>
       <c r="I28" s="82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J28" s="82"/>
       <c r="K28" s="82"/>
       <c r="L28" s="82"/>
       <c r="M28" s="82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N28" s="82"/>
       <c r="O28" s="82"/>
       <c r="P28" s="98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q28" s="98"/>
       <c r="R28" s="98"/>
       <c r="S28" s="98"/>
       <c r="T28" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="U28" s="102"/>
-      <c r="V28" s="103"/>
+        <v>85</v>
+      </c>
+      <c r="U28" s="104"/>
+      <c r="V28" s="105"/>
     </row>
     <row r="29" s="77" customFormat="1" customHeight="1" spans="1:22">
       <c r="A29" s="83">
         <v>1</v>
       </c>
       <c r="B29" s="84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="85"/>
       <c r="D29" s="85"/>
@@ -5804,25 +5821,25 @@
       <c r="F29" s="85"/>
       <c r="G29" s="85"/>
       <c r="H29" s="85"/>
-      <c r="I29" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="154" t="s">
+      <c r="I29" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" s="99"/>
+      <c r="O29" s="99"/>
+      <c r="P29" s="157" t="s">
         <v>87</v>
       </c>
       <c r="Q29" s="83"/>
       <c r="R29" s="83"/>
       <c r="S29" s="83"/>
       <c r="T29" s="83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U29" s="83"/>
       <c r="V29" s="83"/>
@@ -5840,25 +5857,25 @@
       <c r="F30" s="86"/>
       <c r="G30" s="86"/>
       <c r="H30" s="86"/>
-      <c r="I30" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="154" t="s">
-        <v>119</v>
+      <c r="I30" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" s="99"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="157" t="s">
+        <v>118</v>
       </c>
       <c r="Q30" s="83"/>
       <c r="R30" s="83"/>
       <c r="S30" s="83"/>
       <c r="T30" s="83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U30" s="83"/>
       <c r="V30" s="83"/>
@@ -5868,7 +5885,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="91" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" s="90"/>
       <c r="D31" s="90"/>
@@ -5876,25 +5893,25 @@
       <c r="F31" s="90"/>
       <c r="G31" s="90"/>
       <c r="H31" s="97"/>
-      <c r="I31" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
+      <c r="I31" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
       <c r="P31" s="83" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="83"/>
       <c r="R31" s="83"/>
       <c r="S31" s="83"/>
-      <c r="T31" s="154" t="s">
-        <v>127</v>
+      <c r="T31" s="157" t="s">
+        <v>126</v>
       </c>
       <c r="U31" s="83"/>
       <c r="V31" s="83"/>
@@ -5904,7 +5921,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" s="90"/>
       <c r="D32" s="90"/>
@@ -5912,25 +5929,25 @@
       <c r="F32" s="90"/>
       <c r="G32" s="90"/>
       <c r="H32" s="97"/>
-      <c r="I32" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
+      <c r="I32" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
       <c r="P32" s="83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="83"/>
       <c r="R32" s="83"/>
       <c r="S32" s="83"/>
       <c r="T32" s="83" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U32" s="83"/>
       <c r="V32" s="83"/>
@@ -5940,7 +5957,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C33" s="90"/>
       <c r="D33" s="90"/>
@@ -5948,25 +5965,25 @@
       <c r="F33" s="90"/>
       <c r="G33" s="90"/>
       <c r="H33" s="97"/>
-      <c r="I33" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
+      <c r="I33" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="158" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
       <c r="P33" s="83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="83"/>
       <c r="R33" s="83"/>
       <c r="S33" s="83"/>
       <c r="T33" s="83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U33" s="83"/>
       <c r="V33" s="83"/>
@@ -6118,7 +6135,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:22">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6149,7 +6166,7 @@
       <c r="T1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="153" t="s">
+      <c r="U1" s="156" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="63"/>
@@ -6209,7 +6226,7 @@
       <c r="T3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="153" t="s">
+      <c r="U3" s="156" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="63"/>
@@ -6240,7 +6257,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -6252,7 +6269,7 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
@@ -6264,7 +6281,7 @@
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R5" s="13" t="s">
         <v>29</v>
@@ -6282,7 +6299,7 @@
     </row>
     <row r="8" s="65" customFormat="1" customHeight="1" spans="1:1">
       <c r="A8" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" s="65" customFormat="1" customHeight="1" spans="1:1">
@@ -6427,7 +6444,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:17">
       <c r="A1" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -6453,7 +6470,7 @@
         <v>11</v>
       </c>
       <c r="O1" s="37"/>
-      <c r="P1" s="153" t="s">
+      <c r="P1" s="156" t="s">
         <v>12</v>
       </c>
       <c r="Q1" s="63"/>
@@ -6503,7 +6520,7 @@
         <v>17</v>
       </c>
       <c r="O3" s="37"/>
-      <c r="P3" s="153" t="s">
+      <c r="P3" s="156" t="s">
         <v>18</v>
       </c>
       <c r="Q3" s="63"/>
@@ -6529,7 +6546,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -6541,14 +6558,14 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="13" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>29</v>
@@ -6560,7 +6577,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:17">
       <c r="A6" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -6569,7 +6586,7 @@
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I6" s="46"/>
       <c r="J6" s="46"/>
@@ -6578,14 +6595,14 @@
       <c r="M6" s="46"/>
       <c r="N6" s="46"/>
       <c r="O6" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P6" s="46"/>
       <c r="Q6" s="46"/>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="1:17">
       <c r="A7" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -6600,7 +6617,7 @@
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A8" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="20"/>
@@ -6610,7 +6627,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="22"/>
       <c r="I8" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O8" s="26"/>
       <c r="P8" s="21"/>
@@ -6618,7 +6635,7 @@
     </row>
     <row r="9" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A9" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -6629,17 +6646,17 @@
       <c r="H9" s="22"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O9" s="22" t="s">
         <v>144</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>145</v>
       </c>
       <c r="P9" s="21"/>
       <c r="Q9" s="21"/>
     </row>
     <row r="10" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -6650,11 +6667,11 @@
       <c r="H10" s="22"/>
       <c r="I10" s="4"/>
       <c r="J10" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K10" s="49"/>
       <c r="L10" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O10" s="22"/>
       <c r="P10" s="23"/>
@@ -6662,7 +6679,7 @@
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A11" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6673,11 +6690,11 @@
       <c r="H11" s="22"/>
       <c r="I11" s="4"/>
       <c r="J11" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K11" s="52"/>
       <c r="L11" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="23"/>
@@ -6685,7 +6702,7 @@
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A12" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -6696,11 +6713,11 @@
       <c r="H12" s="22"/>
       <c r="I12" s="4"/>
       <c r="J12" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K12" s="52"/>
       <c r="L12" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O12" s="22"/>
       <c r="P12" s="23"/>
@@ -6708,7 +6725,7 @@
     </row>
     <row r="13" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A13" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6723,7 +6740,7 @@
       </c>
       <c r="K13" s="52"/>
       <c r="L13" s="53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O13" s="22"/>
       <c r="P13" s="23"/>
@@ -6731,7 +6748,7 @@
     </row>
     <row r="14" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A14" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -6742,11 +6759,11 @@
       <c r="H14" s="22"/>
       <c r="I14" s="4"/>
       <c r="J14" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K14" s="52"/>
       <c r="L14" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O14" s="22"/>
       <c r="P14" s="23"/>
@@ -6754,7 +6771,7 @@
     </row>
     <row r="15" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A15" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -6764,11 +6781,11 @@
       <c r="G15" s="21"/>
       <c r="H15" s="22"/>
       <c r="J15" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K15" s="52"/>
       <c r="L15" s="53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O15" s="26"/>
       <c r="P15" s="23"/>
@@ -6776,7 +6793,7 @@
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A16" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -6786,11 +6803,11 @@
       <c r="G16" s="23"/>
       <c r="H16" s="22"/>
       <c r="J16" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K16" s="52"/>
       <c r="L16" s="53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" s="22"/>
       <c r="P16" s="23"/>
@@ -6808,7 +6825,7 @@
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A18" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -6818,7 +6835,7 @@
       <c r="G18" s="23"/>
       <c r="H18" s="22"/>
       <c r="I18" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O18" s="22"/>
       <c r="P18" s="21"/>
@@ -6834,7 +6851,7 @@
       <c r="G19" s="23"/>
       <c r="H19" s="22"/>
       <c r="J19" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O19" s="22"/>
       <c r="P19" s="21"/>
@@ -6850,7 +6867,7 @@
       <c r="G20" s="23"/>
       <c r="H20" s="22"/>
       <c r="J20" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O20" s="22"/>
       <c r="P20" s="21"/>
@@ -6866,16 +6883,16 @@
       <c r="G21" s="24"/>
       <c r="H21" s="22"/>
       <c r="J21" s="54" t="s">
+        <v>162</v>
+      </c>
+      <c r="K21" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="K21" s="54" t="s">
+      <c r="L21" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="L21" s="54" t="s">
-        <v>165</v>
-      </c>
       <c r="M21" s="54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O21" s="26"/>
       <c r="P21" s="23"/>
@@ -6891,16 +6908,16 @@
       <c r="G22" s="23"/>
       <c r="H22" s="22"/>
       <c r="J22" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" s="56" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="K22" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="55" t="s">
+      <c r="M22" s="57" t="s">
         <v>167</v>
-      </c>
-      <c r="M22" s="57" t="s">
-        <v>168</v>
       </c>
       <c r="O22" s="26"/>
       <c r="P22" s="23"/>
@@ -6917,13 +6934,13 @@
       <c r="H23" s="22"/>
       <c r="J23" s="55"/>
       <c r="K23" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="L23" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="L23" s="58" t="s">
+      <c r="M23" s="57" t="s">
         <v>170</v>
-      </c>
-      <c r="M23" s="57" t="s">
-        <v>171</v>
       </c>
       <c r="O23" s="26"/>
       <c r="P23" s="21"/>
@@ -6940,13 +6957,13 @@
       <c r="H24" s="22"/>
       <c r="J24" s="55"/>
       <c r="K24" s="56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L24" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="M24" s="57" t="s">
         <v>172</v>
-      </c>
-      <c r="M24" s="57" t="s">
-        <v>173</v>
       </c>
       <c r="O24" s="26"/>
       <c r="P24" s="23"/>
@@ -6963,13 +6980,13 @@
       <c r="H25" s="22"/>
       <c r="J25" s="55"/>
       <c r="K25" s="56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L25" s="58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M25" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O25" s="26"/>
       <c r="P25" s="23"/>
@@ -6986,13 +7003,13 @@
       <c r="H26" s="22"/>
       <c r="J26" s="55"/>
       <c r="K26" s="56" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L26" s="58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M26" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O26" s="26"/>
       <c r="P26" s="23"/>
@@ -7015,10 +7032,10 @@
         <v>95</v>
       </c>
       <c r="L27" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="M27" s="57" t="s">
         <v>176</v>
-      </c>
-      <c r="M27" s="57" t="s">
-        <v>177</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="27"/>
@@ -7040,11 +7057,11 @@
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="1:17">
       <c r="A29" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="3"/>
       <c r="O29" s="18"/>
@@ -7062,7 +7079,7 @@
       <c r="H30" s="18"/>
       <c r="I30" s="3"/>
       <c r="J30" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O30" s="18"/>
       <c r="P30" s="28"/>
@@ -7078,7 +7095,7 @@
       <c r="H31" s="18"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O31" s="27"/>
       <c r="P31" s="28"/>
@@ -7094,11 +7111,11 @@
       <c r="H32" s="18"/>
       <c r="I32" s="3"/>
       <c r="J32" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K32" s="49"/>
       <c r="L32" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M32" s="50"/>
       <c r="O32" s="27"/>
@@ -7115,11 +7132,11 @@
       <c r="H33" s="18"/>
       <c r="I33" s="3"/>
       <c r="J33" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K33" s="59"/>
       <c r="L33" s="60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M33" s="60"/>
       <c r="O33" s="27"/>
@@ -7136,11 +7153,11 @@
       <c r="H34" s="18"/>
       <c r="I34" s="3"/>
       <c r="J34" s="59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K34" s="59"/>
       <c r="L34" s="60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M34" s="60"/>
       <c r="O34" s="27"/>
@@ -7157,11 +7174,11 @@
       <c r="H35" s="18"/>
       <c r="I35" s="3"/>
       <c r="J35" s="59" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K35" s="59"/>
       <c r="L35" s="60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M35" s="60"/>
       <c r="O35" s="27"/>
@@ -7178,11 +7195,11 @@
       <c r="H36" s="18"/>
       <c r="I36" s="3"/>
       <c r="J36" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K36" s="59"/>
       <c r="L36" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M36" s="60"/>
       <c r="O36" s="27"/>
@@ -7199,11 +7216,11 @@
       <c r="H37" s="18"/>
       <c r="I37" s="3"/>
       <c r="J37" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K37" s="59"/>
       <c r="L37" s="60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M37" s="60"/>
       <c r="O37" s="27"/>
@@ -7220,11 +7237,11 @@
       <c r="H38" s="18"/>
       <c r="I38" s="3"/>
       <c r="J38" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K38" s="59"/>
       <c r="L38" s="60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M38" s="60"/>
       <c r="O38" s="27"/>
@@ -7255,7 +7272,7 @@
       <c r="H40" s="18"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O40" s="27"/>
       <c r="P40" s="28"/>
@@ -7270,8 +7287,8 @@
       <c r="G41" s="3"/>
       <c r="H41" s="18"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="155" t="s">
-        <v>192</v>
+      <c r="J41" s="159" t="s">
+        <v>191</v>
       </c>
       <c r="O41" s="27"/>
       <c r="P41" s="28"/>
@@ -7302,7 +7319,7 @@
       <c r="H43" s="18"/>
       <c r="I43" s="4"/>
       <c r="J43" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O43" s="27"/>
       <c r="P43" s="28"/>
@@ -7319,7 +7336,7 @@
       <c r="H44" s="18"/>
       <c r="I44" s="4"/>
       <c r="J44" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O44" s="27"/>
       <c r="P44" s="28"/>
@@ -7350,11 +7367,11 @@
       <c r="G46" s="30"/>
       <c r="H46" s="18"/>
       <c r="I46" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J46" s="3"/>
       <c r="O46" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P46" s="28"/>
       <c r="Q46" s="28"/>
@@ -7370,7 +7387,7 @@
       <c r="H47" s="18"/>
       <c r="I47" s="3"/>
       <c r="J47" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O47" s="18"/>
       <c r="P47" s="28"/>
@@ -7387,11 +7404,11 @@
       <c r="H48" s="18"/>
       <c r="I48" s="3"/>
       <c r="J48" s="48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K48" s="49"/>
       <c r="L48" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M48" s="50"/>
       <c r="O48" s="18"/>
@@ -7413,7 +7430,7 @@
       </c>
       <c r="K49" s="59"/>
       <c r="L49" s="60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M49" s="60"/>
       <c r="O49" s="18"/>
@@ -7431,11 +7448,11 @@
       <c r="H50" s="18"/>
       <c r="I50" s="3"/>
       <c r="J50" s="59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K50" s="59"/>
       <c r="L50" s="60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M50" s="60"/>
       <c r="O50" s="18"/>
@@ -7453,11 +7470,11 @@
       <c r="H51" s="18"/>
       <c r="I51" s="3"/>
       <c r="J51" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K51" s="59"/>
       <c r="L51" s="60" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M51" s="60"/>
       <c r="O51" s="18"/>
@@ -7475,11 +7492,11 @@
       <c r="H52" s="18"/>
       <c r="I52" s="3"/>
       <c r="J52" s="59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K52" s="59"/>
       <c r="L52" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M52" s="60"/>
       <c r="O52" s="18"/>
@@ -7497,11 +7514,11 @@
       <c r="H53" s="18"/>
       <c r="I53" s="3"/>
       <c r="J53" s="59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K53" s="59"/>
       <c r="L53" s="60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M53" s="60"/>
       <c r="O53" s="18"/>
@@ -7519,11 +7536,11 @@
       <c r="H54" s="18"/>
       <c r="I54" s="3"/>
       <c r="J54" s="59" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K54" s="59"/>
       <c r="L54" s="60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M54" s="60"/>
       <c r="O54" s="18"/>
@@ -7551,14 +7568,14 @@
     </row>
     <row r="56" s="3" customFormat="1" customHeight="1" spans="1:17">
       <c r="A56" s="22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H56" s="22"/>
       <c r="I56" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="O56" s="26" t="s">
         <v>199</v>
-      </c>
-      <c r="O56" s="26" t="s">
-        <v>200</v>
       </c>
       <c r="P56" s="23"/>
       <c r="Q56" s="23"/>
@@ -7574,7 +7591,7 @@
       <c r="H57" s="18"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
@@ -7588,13 +7605,13 @@
       <c r="A58" s="22"/>
       <c r="H58" s="22"/>
       <c r="J58" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="K58" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="K58" s="50" t="s">
-        <v>203</v>
-      </c>
       <c r="L58" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O58" s="26"/>
       <c r="P58" s="23"/>
@@ -7604,7 +7621,7 @@
       <c r="A59" s="22"/>
       <c r="H59" s="22"/>
       <c r="J59" s="51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K59" s="53" t="s">
         <v>95</v>
@@ -7626,7 +7643,7 @@
         <v>95</v>
       </c>
       <c r="L60" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O60" s="26"/>
       <c r="P60" s="23"/>
@@ -7638,13 +7655,13 @@
         <v>92</v>
       </c>
       <c r="K61" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="L61" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="L61" s="53" t="s">
+      <c r="O61" s="26" t="s">
         <v>206</v>
-      </c>
-      <c r="O61" s="26" t="s">
-        <v>207</v>
       </c>
       <c r="P61" s="23"/>
       <c r="Q61" s="23"/>
@@ -7654,10 +7671,10 @@
       <c r="H62" s="22"/>
       <c r="J62" s="60"/>
       <c r="K62" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="L62" s="53" t="s">
         <v>208</v>
-      </c>
-      <c r="L62" s="53" t="s">
-        <v>209</v>
       </c>
       <c r="O62" s="22"/>
       <c r="P62" s="23"/>
@@ -7675,10 +7692,10 @@
       <c r="H64" s="22"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O64" s="22"/>
       <c r="P64" s="23"/>
@@ -7689,13 +7706,13 @@
       <c r="H65" s="22"/>
       <c r="I65" s="2"/>
       <c r="J65" s="48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L65" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -7707,7 +7724,7 @@
       <c r="A66" s="22"/>
       <c r="H66" s="22"/>
       <c r="J66" s="51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K66" s="53" t="s">
         <v>95</v>
@@ -7731,7 +7748,7 @@
         <v>95</v>
       </c>
       <c r="L67" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -7750,7 +7767,7 @@
         <v>96</v>
       </c>
       <c r="L68" s="53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -7764,7 +7781,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="60"/>
       <c r="K69" s="53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L69" s="59">
         <v>0</v>
